--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.84.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.84.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -871,7 +871,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.84.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.84.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,13 +431,13 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="50" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="29" customWidth="1" min="19" max="19"/>
+    <col width="60" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
     <col width="29" customWidth="1" min="21" max="21"/>
     <col width="31" customWidth="1" min="22" max="22"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.84.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.84.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0084.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0084.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -613,16 +613,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L51: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: ã€� 4</t>
+          <t>L49: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L29: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: is to be set down toâ€™ be heard ; and the Court, if it so, made,</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L13: isolated marker/symbol line :: 77</t>
@@ -630,7 +634,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L1: isolated marker/symbol line :: ï»¿</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -640,7 +644,11 @@
       </c>
       <c r="Q2" s="1" t="inlineStr"/>
       <c r="R2" s="1" t="inlineStr"/>
-      <c r="S2" s="1" t="inlineStr"/>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>L44: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • by himself or his own solicitor, or upon notice served up-</t>
+        </is>
+      </c>
       <c r="T2" s="1" t="inlineStr"/>
       <c r="U2" s="1" t="inlineStr"/>
       <c r="V2" s="1" t="inlineStr"/>
@@ -661,7 +669,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>81</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -681,7 +689,7 @@
       <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L44: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ by himself or his own solicitor, or upon notice served up-</t>
+          <t>L44: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • by himself or his own solicitor, or upon notice served up-</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -740,7 +748,7 @@
       <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L61: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: 550.â€�</t>
+          <t>L101: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -752,7 +760,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L101: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L61: symbol-only separator/garbage line :: 550.”</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -774,12 +782,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -797,11 +805,7 @@
         </is>
       </c>
       <c r="J5" s="1" t="inlineStr"/>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L101: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
@@ -809,7 +813,11 @@
           <t>L48: isolated marker/symbol line :: 2</t>
         </is>
       </c>
-      <c r="O5" s="1" t="inlineStr"/>
+      <c r="O5" s="1" t="inlineStr">
+        <is>
+          <t>L101: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
       <c r="P5" s="1" t="inlineStr"/>
       <c r="Q5" s="1" t="inlineStr"/>
       <c r="R5" s="1" t="inlineStr"/>
@@ -853,7 +861,7 @@
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L50: isolated marker/symbol line :: *</t>
+          <t>L49: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr"/>
@@ -900,7 +908,7 @@
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L69: symbol-only separator/garbage line :: 850."</t>
+          <t>L50: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr"/>
@@ -947,7 +955,7 @@
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L70: isolated marker/symbol line :: .</t>
+          <t>L51: isolated marker/symbol line :: 、 4</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr"/>
@@ -990,7 +998,7 @@
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L72: isolated marker/symbol line :: 6</t>
+          <t>L69: symbol-only separator/garbage line :: 850."</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr"/>
@@ -1018,7 +1026,7 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1033,7 +1041,7 @@
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L76: isolated marker/symbol line :: 2</t>
+          <t>L70: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr"/>
@@ -1061,7 +1069,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1076,7 +1084,7 @@
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L77: isolated marker/symbol line :: e</t>
+          <t>L72: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr"/>
@@ -1099,12 +1107,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1117,7 +1125,11 @@
       <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
-      <c r="N12" s="1" t="inlineStr"/>
+      <c r="N12" s="1" t="inlineStr">
+        <is>
+          <t>L76: isolated marker/symbol line :: 2</t>
+        </is>
+      </c>
       <c r="O12" s="1" t="inlineStr"/>
       <c r="P12" s="1" t="inlineStr"/>
       <c r="Q12" s="1" t="inlineStr"/>
@@ -1156,7 +1168,11 @@
       <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
-      <c r="N13" s="1" t="inlineStr"/>
+      <c r="N13" s="1" t="inlineStr">
+        <is>
+          <t>L77: isolated marker/symbol line :: e</t>
+        </is>
+      </c>
       <c r="O13" s="1" t="inlineStr"/>
       <c r="P13" s="1" t="inlineStr"/>
       <c r="Q13" s="1" t="inlineStr"/>
@@ -1182,7 +1198,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
